--- a/Arquivos/Atividade_Avaliativa2_16_09.xlsx
+++ b/Arquivos/Atividade_Avaliativa2_16_09.xlsx
@@ -8,106 +8,137 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17726E19-9B5A-4FE3-AB12-B321F9B267F7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C541F5-6969-4927-B44A-030D60D5A20F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{759A8800-CD47-4849-AA2E-61C2ECE26B63}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{759A8800-CD47-4849-AA2E-61C2ECE26B63}"/>
   </bookViews>
   <sheets>
     <sheet name="EX1" sheetId="6" r:id="rId1"/>
-    <sheet name="EX3" sheetId="7" r:id="rId2"/>
-    <sheet name="EX4" sheetId="8" r:id="rId3"/>
+    <sheet name="EX2" sheetId="9" r:id="rId2"/>
+    <sheet name="EX3" sheetId="7" r:id="rId3"/>
+    <sheet name="EX4" sheetId="8" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'EX1'!$B$2:$D$2</definedName>
-    <definedName name="solver_adj" localSheetId="1" hidden="1">'EX3'!$B$2:$C$2</definedName>
-    <definedName name="solver_adj" localSheetId="2" hidden="1">'EX4'!$B$2:$C$2</definedName>
+    <definedName name="solver_adj" localSheetId="1" hidden="1">'EX2'!$B$2:$D$2</definedName>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">'EX3'!$B$2:$C$2</definedName>
+    <definedName name="solver_adj" localSheetId="3" hidden="1">'EX4'!$B$2:$D$2</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="3" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'EX1'!$E$7:$E$9</definedName>
-    <definedName name="solver_lhs1" localSheetId="1" hidden="1">'EX3'!$D$7:$D$8</definedName>
-    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'EX4'!$D$7:$D$8</definedName>
+    <definedName name="solver_lhs1" localSheetId="1" hidden="1">'EX2'!$E$7:$E$9</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'EX3'!$D$7:$D$8</definedName>
+    <definedName name="solver_lhs1" localSheetId="3" hidden="1">'EX4'!$E$7:$E$9</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="3" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="3" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'EX1'!$B$4</definedName>
-    <definedName name="solver_opt" localSheetId="1" hidden="1">'EX3'!$B$4</definedName>
-    <definedName name="solver_opt" localSheetId="2" hidden="1">'EX4'!$B$4</definedName>
+    <definedName name="solver_opt" localSheetId="1" hidden="1">'EX2'!$B$4</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">'EX3'!$B$4</definedName>
+    <definedName name="solver_opt" localSheetId="3" hidden="1">'EX4'!$B$4</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="3" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">'EX1'!$F$7:$F$9</definedName>
-    <definedName name="solver_rhs1" localSheetId="1" hidden="1">'EX3'!$E$7:$E$8</definedName>
-    <definedName name="solver_rhs1" localSheetId="2" hidden="1">'EX4'!$E$7:$E$8</definedName>
+    <definedName name="solver_rhs1" localSheetId="1" hidden="1">'EX2'!$F$7:$F$9</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">'EX3'!$E$7:$E$8</definedName>
+    <definedName name="solver_rhs1" localSheetId="3" hidden="1">'EX4'!$F$7:$F$9</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="3" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="3" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_typ" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -207,7 +238,7 @@
     <author>Fatec</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{425126D6-5C33-4C7F-8B70-D128356E7E14}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{7911FB52-0F03-4462-9EA0-0C03305E31A6}">
       <text>
         <r>
           <rPr>
@@ -231,7 +262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{08E37327-41BE-437E-AC94-23E4E623FD85}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{C1C5060A-23C4-45DB-BAB3-A51A18E863A0}">
       <text>
         <r>
           <rPr>
@@ -255,7 +286,80 @@
         </r>
       </text>
     </comment>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{535C3D15-DDAE-4C12-B769-D3520156D39E}">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{56801E04-D332-47DB-9F13-245D67AB431C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Fatec:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Restrição 1 * Variável 1 + Restrição 2 * Variável 2 + Restrição 3 * Variável 3.
+Linhas seguintes: Travar as variáveis e seguir com as restrições 2,3,4...</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A15" authorId="0" shapeId="0" xr:uid="{41939CC0-0EF9-4709-B95A-68B22117000D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Fatec:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>O valor das variáveis será preenchido pelo Solver. O Solver é acessado na aba: Dados &gt; Solver.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A16" authorId="0" shapeId="0" xr:uid="{7077E446-19E1-4238-9848-94EFB96E28B3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Fatec:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Informar lucro de cada variável.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{E2DB7259-2095-427F-98F0-8CBCA9A92DB6}">
       <text>
         <r>
           <rPr>
@@ -290,6 +394,89 @@
     <author>Fatec</author>
   </authors>
   <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{425126D6-5C33-4C7F-8B70-D128356E7E14}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Fatec:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>O valor das variáveis será preenchido pelo Solver. O Solver é acessado na aba: Dados &gt; Solver.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{08E37327-41BE-437E-AC94-23E4E623FD85}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Fatec:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Informar lucro de cada variável.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{535C3D15-DDAE-4C12-B769-D3520156D39E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Fatec:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Restrição 1 * Variável 1 + Restrição 2 * Variável 2 + Restrição 3 * Variável 3.
+Linhas seguintes: Travar as variáveis e seguir com as restrições 2,3,4...</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Fatec</author>
+  </authors>
+  <commentList>
     <comment ref="A2" authorId="0" shapeId="0" xr:uid="{319BB51A-62F0-4828-96AF-1C33200FC998}">
       <text>
         <r>
@@ -338,7 +525,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{61FE44E0-97E5-423A-B69D-672202332A0C}">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{61FE44E0-97E5-423A-B69D-672202332A0C}">
       <text>
         <r>
           <rPr>
@@ -368,7 +555,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="29">
   <si>
     <t>Quantidade:</t>
   </si>
@@ -419,13 +606,52 @@
   </si>
   <si>
     <t>Não refrigerado</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>Colômbia</t>
+  </si>
+  <si>
+    <t>Peru</t>
+  </si>
+  <si>
+    <t>Aroma</t>
+  </si>
+  <si>
+    <t>Intensidade</t>
+  </si>
+  <si>
+    <t>Quantidade (kg)</t>
+  </si>
+  <si>
+    <t>Verde</t>
+  </si>
+  <si>
+    <t>Azul</t>
+  </si>
+  <si>
+    <t>Comum</t>
+  </si>
+  <si>
+    <t>G. Pura</t>
+  </si>
+  <si>
+    <t>G. Octana</t>
+  </si>
+  <si>
+    <t>Aditivo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -455,6 +681,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -503,11 +736,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -518,9 +752,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Bom" xfId="1" builtinId="26"/>
+    <cellStyle name="Moeda" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -972,6 +1212,293 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A41DFCF-1D81-413F-9EB9-53F1649E20D5}">
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0</v>
+      </c>
+      <c r="C2" s="8">
+        <v>11056910.569105688</v>
+      </c>
+      <c r="D2" s="8">
+        <v>5203252.0325203277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="6">
+        <f>SUMPRODUCT(B2:D2,B3:D3)</f>
+        <v>3804878.0487804879</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.52</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.74</v>
+      </c>
+      <c r="E7" s="8">
+        <f>SUMPRODUCT(B7:D7,$B$2:$D$2)</f>
+        <v>9600000</v>
+      </c>
+      <c r="F7" s="7">
+        <v>9600000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E8" s="8">
+        <f t="shared" ref="E8" si="0">SUMPRODUCT(B8:D8,$B$2:$D$2)</f>
+        <v>4800000</v>
+      </c>
+      <c r="F8" s="7">
+        <v>4800000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="E9" s="8">
+        <f>SUMPRODUCT(B9:D9,$B$2:$D$2)</f>
+        <v>1860162.6016260162</v>
+      </c>
+      <c r="F9" s="7">
+        <v>2200000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="6">
+        <f>SUMPRODUCT(B15:D15,B16:D16)</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="8">
+        <f>SUMPRODUCT(B20:D20,$B$2:$D$2)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="8">
+        <f t="shared" ref="E21" si="1">SUMPRODUCT(B21:D21,$B$2:$D$2)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="8">
+        <f>SUMPRODUCT(B22:D22,$B$2:$D$2)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C67C76F-F4D2-48BB-A98F-18835D00FFAA}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1083,110 +1610,152 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC536746-45B2-4350-BDF5-97F0D4C77E22}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>15</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="C2" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="1">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C3" s="1">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.6</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5">
-        <f>SUMPRODUCT(B2:C2,B3:C3)</f>
-        <v>12.5</v>
+      <c r="B4" s="6">
+        <f>SUMPRODUCT(B2:D2,B3:D3)</f>
+        <v>1.3333333333333333</v>
       </c>
       <c r="C4" s="5"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D4" s="5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>14</v>
+      <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="3">
+        <v>75</v>
+      </c>
+      <c r="C7" s="3">
+        <v>60</v>
+      </c>
+      <c r="D7" s="3">
+        <v>85</v>
+      </c>
+      <c r="E7" s="2">
+        <f>SUMPRODUCT(B7:D7,$B$2:$D$2)</f>
+        <v>200</v>
+      </c>
+      <c r="F7" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="3">
         <v>15</v>
       </c>
-      <c r="B7" s="3">
-        <v>2</v>
-      </c>
-      <c r="C7" s="3">
-        <v>3</v>
-      </c>
-      <c r="D7" s="2">
-        <f>SUMPRODUCT(B7:C7,$B$2:$C$2)</f>
-        <v>90</v>
-      </c>
-      <c r="E7" s="3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="3">
+        <v>20</v>
+      </c>
+      <c r="D8" s="3">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" ref="E8:E9" si="0">SUMPRODUCT(B8:D8,$B$2:$D$2)</f>
+        <v>40</v>
+      </c>
+      <c r="F8" s="3">
         <v>16</v>
       </c>
-      <c r="B8" s="3">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3">
-        <v>3</v>
-      </c>
-      <c r="D8" s="2">
-        <f>SUMPRODUCT(B8:C8,$B$2:$C$2)</f>
-        <v>120</v>
-      </c>
-      <c r="E8" s="3">
-        <v>120</v>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="2">
+        <f>SUMPRODUCT(B9:D9,$B$2:$D$2)</f>
+        <v>4000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>4000</v>
       </c>
     </row>
   </sheetData>
